--- a/Proyecto Intermodular/Tema2/Ejercicio1.xlsx
+++ b/Proyecto Intermodular/Tema2/Ejercicio1.xlsx
@@ -79,11 +79,10 @@
     </font>
     <font>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -98,12 +97,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor theme="7" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEB3E6"/>
+        <bgColor rgb="FFDEB3E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor theme="9" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor theme="5" tint="-0.249977111117893"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor theme="4" tint="0.39997558519241921"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor theme="4" tint="-0.249977111117893"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="39">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -200,6 +229,82 @@
         <color theme="1"/>
       </left>
       <right style="none"/>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="dashDot">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="dashDot">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="dashDot">
+        <color theme="1"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="dashDot">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
       <top style="hair">
         <color theme="1"/>
       </top>
@@ -219,6 +324,61 @@
       <bottom style="hair">
         <color theme="1"/>
       </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="dashDot">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="dashDot">
+        <color theme="1"/>
+      </top>
+      <bottom style="dashDot">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="dashDot">
+        <color theme="1"/>
+      </right>
+      <top style="dashDot">
+        <color theme="1"/>
+      </top>
+      <bottom style="dashDot">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -246,118 +406,183 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="hair">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="dashed">
         <color theme="1"/>
       </left>
       <right style="none"/>
-      <top style="hair">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="dashDotDot">
-        <color theme="4" tint="-0.499984740745262"/>
-      </left>
-      <right style="none"/>
-      <top style="dashDotDot">
-        <color theme="4" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color theme="4" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="dashDotDot">
-        <color theme="4" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color theme="4" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="dashDotDot">
-        <color theme="4" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color theme="4" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="dashDotDot">
-        <color theme="4" tint="-0.499984740745262"/>
-      </right>
-      <top style="dashDotDot">
-        <color theme="4" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="dashDotDot">
-        <color theme="4" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="hair">
-        <color theme="1"/>
-      </top>
-      <bottom style="thick">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="hair">
-        <color theme="1"/>
-      </top>
-      <bottom style="thick">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="hair">
-        <color theme="1"/>
-      </top>
-      <bottom style="thick">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thick">
+      <top style="none"/>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="dashDot">
+        <color theme="1"/>
+      </top>
+      <bottom style="dashDot">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="dashed">
         <color theme="1"/>
       </right>
       <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="dashDot">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="dashDot">
+        <color theme="1"/>
+      </top>
+      <bottom style="dashDot">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="dashDot">
+        <color theme="1"/>
+      </left>
+      <right style="dashDot">
+        <color theme="1"/>
+      </right>
+      <top style="dashDot">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="dashDot">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="dashDot">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="dashDot">
+        <color theme="1"/>
+      </right>
+      <top style="dashDot">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="1"/>
+      </left>
+      <right style="dashDot">
+        <color theme="1"/>
+      </right>
+      <top style="dashDot">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="dashDot">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="dashDot">
         <color theme="1"/>
       </top>
       <bottom style="thick">
@@ -369,7 +594,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="54">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -399,22 +624,51 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="2" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="24" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="25" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="25" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="7" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="7" borderId="25" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="7" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="7" borderId="28" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="7" borderId="29" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="33" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="36" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="37" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="38" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="3" wrapText="1"/>
     </xf>
@@ -1100,251 +1354,251 @@
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
       <c r="K4" s="10"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
       <c r="O4" s="10"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
       <c r="S4" s="10"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
       <c r="W4" s="10"/>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="11"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
       <c r="AA4" s="10"/>
-      <c r="AB4" s="11"/>
-      <c r="AC4" s="11"/>
-      <c r="AD4" s="11"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="15"/>
       <c r="AE4" s="10"/>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="11"/>
-      <c r="AH4" s="11"/>
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="15"/>
+      <c r="AH4" s="15"/>
       <c r="AI4" s="10"/>
-      <c r="AJ4" s="11"/>
-      <c r="AK4" s="11"/>
-      <c r="AL4" s="12"/>
+      <c r="AJ4" s="15"/>
+      <c r="AK4" s="15"/>
+      <c r="AL4" s="16"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="11"/>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11"/>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="10"/>
-      <c r="AF5" s="11"/>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="10"/>
-      <c r="AJ5" s="11"/>
-      <c r="AK5" s="11"/>
-      <c r="AL5" s="12"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24"/>
+      <c r="AA5" s="18"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="24"/>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="18"/>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="18"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
+      <c r="AL5" s="25"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="10"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="11"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="10"/>
-      <c r="AF6" s="11"/>
-      <c r="AG6" s="11"/>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="10"/>
-      <c r="AJ6" s="11"/>
-      <c r="AK6" s="11"/>
-      <c r="AL6" s="12"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="22"/>
+      <c r="AE6" s="23"/>
+      <c r="AF6" s="22"/>
+      <c r="AG6" s="22"/>
+      <c r="AH6" s="22"/>
+      <c r="AI6" s="23"/>
+      <c r="AJ6" s="24"/>
+      <c r="AK6" s="24"/>
+      <c r="AL6" s="25"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="10"/>
-      <c r="AF7" s="11"/>
-      <c r="AG7" s="11"/>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="10"/>
-      <c r="AJ7" s="11"/>
-      <c r="AK7" s="11"/>
-      <c r="AL7" s="12"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="23"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="31"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="33"/>
+      <c r="AE7" s="23"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="31"/>
+      <c r="AH7" s="32"/>
+      <c r="AI7" s="32"/>
+      <c r="AJ7" s="22"/>
+      <c r="AK7" s="22"/>
+      <c r="AL7" s="34"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="18"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="10"/>
-      <c r="AF8" s="11"/>
-      <c r="AG8" s="11"/>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="10"/>
-      <c r="AJ8" s="11"/>
-      <c r="AK8" s="11"/>
-      <c r="AL8" s="12"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="36"/>
+      <c r="W8" s="37"/>
+      <c r="X8" s="37"/>
+      <c r="Y8" s="37"/>
+      <c r="Z8" s="37"/>
+      <c r="AA8" s="26"/>
+      <c r="AB8" s="19"/>
+      <c r="AC8" s="35"/>
+      <c r="AD8" s="36"/>
+      <c r="AE8" s="38"/>
+      <c r="AF8" s="19"/>
+      <c r="AG8" s="35"/>
+      <c r="AH8" s="35"/>
+      <c r="AI8" s="36"/>
+      <c r="AJ8" s="37"/>
+      <c r="AK8" s="39"/>
+      <c r="AL8" s="40"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="21"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="21"/>
-      <c r="AD9" s="21"/>
-      <c r="AE9" s="20"/>
-      <c r="AF9" s="21"/>
-      <c r="AG9" s="21"/>
-      <c r="AH9" s="21"/>
-      <c r="AI9" s="20"/>
-      <c r="AJ9" s="21"/>
-      <c r="AK9" s="21"/>
-      <c r="AL9" s="24"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="47"/>
+      <c r="W9" s="48"/>
+      <c r="X9" s="47"/>
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="46"/>
+      <c r="AA9" s="47"/>
+      <c r="AB9" s="43"/>
+      <c r="AC9" s="49"/>
+      <c r="AD9" s="47"/>
+      <c r="AE9" s="49"/>
+      <c r="AF9" s="43"/>
+      <c r="AG9" s="50"/>
+      <c r="AH9" s="43"/>
+      <c r="AI9" s="49"/>
+      <c r="AJ9" s="47"/>
+      <c r="AK9" s="50"/>
+      <c r="AL9" s="51"/>
     </row>
     <row r="11" ht="15">
-      <c r="B11" s="25"/>
+      <c r="B11" s="52"/>
     </row>
     <row r="14" ht="14.25">
-      <c r="G14" s="26"/>
+      <c r="G14" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="10">
